--- a/entregables/factor_macro_simple.xlsx
+++ b/entregables/factor_macro_simple.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Datos'!$A$5:$K$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Datos'!$A$5:$N$113</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,7 +22,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,8 +60,24 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <color rgb="00888888"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -115,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -129,13 +145,16 @@
     <xf numFmtId="17" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -501,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K125"/>
+  <dimension ref="A1:N128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -514,7 +533,10 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -591,6 +613,21 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
+          <t>n IBK</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>n SS.FF.</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>COVID</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>origen</t>
         </is>
       </c>
@@ -638,6 +675,21 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
+          <t>Altas de IBK del mes. Con n chico la RD es ruidosa: en 202004 son 15 casos.</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>Altas de las 5 entidades del mes.</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>SI = mes de 2020. El pipeline excluye todo 2020 de la LRA y de rho, y las cifras publicadas de correlacion tambien lo excluyen. Se dejan en la tabla para que la serie no tenga huecos, pero conviene marcarlos en el grafico.</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
           <t>De donde sale la inflacion de esa fila.</t>
         </is>
       </c>
@@ -652,7 +704,7 @@
         <v>43497</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>0.196233</v>
+        <v>0.203226</v>
       </c>
       <c r="I7" s="8" t="n">
         <v>0.159756</v>
@@ -660,7 +712,13 @@
       <c r="J7" s="8" t="n">
         <v>0.143552</v>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="K7" s="9" t="n">
+        <v>4751</v>
+      </c>
+      <c r="L7" s="9" t="n">
+        <v>20564</v>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -676,7 +734,7 @@
         <v>43525</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>0.199458</v>
+        <v>0.206451</v>
       </c>
       <c r="I8" s="8" t="n">
         <v>0.162753</v>
@@ -684,7 +742,13 @@
       <c r="J8" s="8" t="n">
         <v>0.15182</v>
       </c>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="K8" s="9" t="n">
+        <v>5493</v>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>22968</v>
+      </c>
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -700,7 +764,7 @@
         <v>43556</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>0.151755</v>
+        <v>0.158747</v>
       </c>
       <c r="I9" s="8" t="n">
         <v>0.162624</v>
@@ -708,7 +772,13 @@
       <c r="J9" s="8" t="n">
         <v>0.166324</v>
       </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="K9" s="9" t="n">
+        <v>5442</v>
+      </c>
+      <c r="L9" s="9" t="n">
+        <v>23815</v>
+      </c>
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -724,7 +794,7 @@
         <v>43586</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>0.14986</v>
+        <v>0.156853</v>
       </c>
       <c r="I10" s="8" t="n">
         <v>0.157256</v>
@@ -732,7 +802,13 @@
       <c r="J10" s="8" t="n">
         <v>0.166423</v>
       </c>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="K10" s="9" t="n">
+        <v>4941</v>
+      </c>
+      <c r="L10" s="9" t="n">
+        <v>26655</v>
+      </c>
+      <c r="N10" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -748,7 +824,7 @@
         <v>43617</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.09858599999999999</v>
+        <v>0.105579</v>
       </c>
       <c r="I11" s="8" t="n">
         <v>0.13668</v>
@@ -756,7 +832,13 @@
       <c r="J11" s="8" t="n">
         <v>0.157652</v>
       </c>
-      <c r="K11" s="9" t="inlineStr">
+      <c r="K11" s="9" t="n">
+        <v>4602</v>
+      </c>
+      <c r="L11" s="9" t="n">
+        <v>22537</v>
+      </c>
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -772,7 +854,7 @@
         <v>43647</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0.06356299999999999</v>
+        <v>0.07055599999999999</v>
       </c>
       <c r="I12" s="8" t="n">
         <v>0.133944</v>
@@ -780,7 +862,13 @@
       <c r="J12" s="8" t="n">
         <v>0.154797</v>
       </c>
-      <c r="K12" s="9" t="inlineStr">
+      <c r="K12" s="9" t="n">
+        <v>4696</v>
+      </c>
+      <c r="L12" s="9" t="n">
+        <v>25007</v>
+      </c>
+      <c r="N12" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -796,7 +884,7 @@
         <v>43678</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0.010273</v>
+        <v>0.017266</v>
       </c>
       <c r="I13" s="8" t="n">
         <v>0.107168</v>
@@ -804,7 +892,13 @@
       <c r="J13" s="8" t="n">
         <v>0.142713</v>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="K13" s="9" t="n">
+        <v>4255</v>
+      </c>
+      <c r="L13" s="9" t="n">
+        <v>24721</v>
+      </c>
+      <c r="N13" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -820,7 +914,7 @@
         <v>43709</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0.063736</v>
+        <v>0.070729</v>
       </c>
       <c r="I14" s="8" t="n">
         <v>0.114357</v>
@@ -828,7 +922,13 @@
       <c r="J14" s="8" t="n">
         <v>0.14481</v>
       </c>
-      <c r="K14" s="9" t="inlineStr">
+      <c r="K14" s="9" t="n">
+        <v>4381</v>
+      </c>
+      <c r="L14" s="9" t="n">
+        <v>25019</v>
+      </c>
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -844,7 +944,7 @@
         <v>43739</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>0.084548</v>
+        <v>0.091541</v>
       </c>
       <c r="I15" s="8" t="n">
         <v>0.138146</v>
@@ -852,7 +952,13 @@
       <c r="J15" s="8" t="n">
         <v>0.147387</v>
       </c>
-      <c r="K15" s="9" t="inlineStr">
+      <c r="K15" s="9" t="n">
+        <v>4003</v>
+      </c>
+      <c r="L15" s="9" t="n">
+        <v>24093</v>
+      </c>
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -868,7 +974,7 @@
         <v>43770</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0.145214</v>
+        <v>0.152207</v>
       </c>
       <c r="I16" s="8" t="n">
         <v>0.141261</v>
@@ -876,7 +982,13 @@
       <c r="J16" s="8" t="n">
         <v>0.163519</v>
       </c>
-      <c r="K16" s="9" t="inlineStr">
+      <c r="K16" s="9" t="n">
+        <v>3044</v>
+      </c>
+      <c r="L16" s="9" t="n">
+        <v>25306</v>
+      </c>
+      <c r="N16" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -892,7 +1004,7 @@
         <v>43800</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>0.217291</v>
+        <v>0.224284</v>
       </c>
       <c r="I17" s="8" t="n">
         <v>0.14006</v>
@@ -900,7 +1012,13 @@
       <c r="J17" s="8" t="n">
         <v>0.173617</v>
       </c>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="K17" s="9" t="n">
+        <v>3013</v>
+      </c>
+      <c r="L17" s="9" t="n">
+        <v>23166</v>
+      </c>
+      <c r="N17" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -916,7 +1034,7 @@
         <v>43831</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>0.16416</v>
+        <v>0.171152</v>
       </c>
       <c r="I18" s="8" t="n">
         <v>0.121631</v>
@@ -924,7 +1042,18 @@
       <c r="J18" s="8" t="n">
         <v>0.149081</v>
       </c>
-      <c r="K18" s="9" t="inlineStr">
+      <c r="K18" s="9" t="n">
+        <v>2968</v>
+      </c>
+      <c r="L18" s="9" t="n">
+        <v>22518</v>
+      </c>
+      <c r="M18" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N18" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -943,9 +1072,9 @@
         <v>-0.157464</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>0.135516</v>
-      </c>
-      <c r="E19" s="10" t="n">
+        <v>0.142509</v>
+      </c>
+      <c r="E19" s="12" t="n">
         <v>1.904</v>
       </c>
       <c r="I19" s="8" t="n">
@@ -954,7 +1083,18 @@
       <c r="J19" s="8" t="n">
         <v>0.148538</v>
       </c>
-      <c r="K19" s="9" t="inlineStr">
+      <c r="K19" s="9" t="n">
+        <v>2424</v>
+      </c>
+      <c r="L19" s="9" t="n">
+        <v>20042</v>
+      </c>
+      <c r="M19" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N19" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -973,9 +1113,9 @@
         <v>-0.162422</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.128921</v>
-      </c>
-      <c r="E20" s="10" t="n">
+        <v>0.135914</v>
+      </c>
+      <c r="E20" s="12" t="n">
         <v>1.8215</v>
       </c>
       <c r="I20" s="8" t="n">
@@ -984,7 +1124,18 @@
       <c r="J20" s="8" t="n">
         <v>0.138422</v>
       </c>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="K20" s="9" t="n">
+        <v>1384</v>
+      </c>
+      <c r="L20" s="9" t="n">
+        <v>10887</v>
+      </c>
+      <c r="M20" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N20" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1002,10 +1153,30 @@
       <c r="C21" s="7" t="n">
         <v>-0.168254</v>
       </c>
-      <c r="E21" s="10" t="n">
+      <c r="D21" s="7" t="n">
+        <v>0.163453</v>
+      </c>
+      <c r="E21" s="12" t="n">
         <v>1.7245</v>
       </c>
-      <c r="K21" s="9" t="inlineStr">
+      <c r="I21" s="8" t="n">
+        <v>0.066667</v>
+      </c>
+      <c r="J21" s="8" t="n">
+        <v>0.133047</v>
+      </c>
+      <c r="K21" s="13" t="n">
+        <v>15</v>
+      </c>
+      <c r="L21" s="9" t="n">
+        <v>932</v>
+      </c>
+      <c r="M21" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N21" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1023,10 +1194,30 @@
       <c r="C22" s="7" t="n">
         <v>-0.164803</v>
       </c>
-      <c r="E22" s="10" t="n">
+      <c r="D22" s="7" t="n">
+        <v>-0.158113</v>
+      </c>
+      <c r="E22" s="12" t="n">
         <v>1.7819</v>
       </c>
-      <c r="K22" s="9" t="inlineStr">
+      <c r="I22" s="8" t="n">
+        <v>0.06818200000000001</v>
+      </c>
+      <c r="J22" s="8" t="n">
+        <v>0.059327</v>
+      </c>
+      <c r="K22" s="13" t="n">
+        <v>44</v>
+      </c>
+      <c r="L22" s="9" t="n">
+        <v>1871</v>
+      </c>
+      <c r="M22" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N22" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1044,10 +1235,30 @@
       <c r="C23" s="7" t="n">
         <v>-0.175812</v>
       </c>
-      <c r="E23" s="10" t="n">
+      <c r="D23" s="7" t="n">
+        <v>-0.016508</v>
+      </c>
+      <c r="E23" s="12" t="n">
         <v>1.5987</v>
       </c>
-      <c r="K23" s="9" t="inlineStr">
+      <c r="I23" s="8" t="n">
+        <v>0.08860800000000001</v>
+      </c>
+      <c r="J23" s="8" t="n">
+        <v>0.073298</v>
+      </c>
+      <c r="K23" s="13" t="n">
+        <v>79</v>
+      </c>
+      <c r="L23" s="9" t="n">
+        <v>1528</v>
+      </c>
+      <c r="M23" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N23" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1066,9 +1277,9 @@
         <v>-0.160008</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>-0.196441</v>
-      </c>
-      <c r="E24" s="10" t="n">
+        <v>-0.189448</v>
+      </c>
+      <c r="E24" s="12" t="n">
         <v>1.8617</v>
       </c>
       <c r="I24" s="8" t="n">
@@ -1077,7 +1288,18 @@
       <c r="J24" s="8" t="n">
         <v>0.045295</v>
       </c>
-      <c r="K24" s="9" t="inlineStr">
+      <c r="K24" s="9" t="n">
+        <v>139</v>
+      </c>
+      <c r="L24" s="9" t="n">
+        <v>3135</v>
+      </c>
+      <c r="M24" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N24" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1095,7 +1317,10 @@
       <c r="C25" s="7" t="n">
         <v>-0.170484</v>
       </c>
-      <c r="E25" s="10" t="n">
+      <c r="D25" s="7" t="n">
+        <v>-0.257976</v>
+      </c>
+      <c r="E25" s="12" t="n">
         <v>1.6874</v>
       </c>
       <c r="I25" s="8" t="n">
@@ -1104,7 +1329,18 @@
       <c r="J25" s="8" t="n">
         <v>0.041494</v>
       </c>
-      <c r="K25" s="9" t="inlineStr">
+      <c r="K25" s="9" t="n">
+        <v>520</v>
+      </c>
+      <c r="L25" s="9" t="n">
+        <v>5543</v>
+      </c>
+      <c r="M25" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N25" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1122,7 +1358,10 @@
       <c r="C26" s="7" t="n">
         <v>-0.162541</v>
       </c>
-      <c r="E26" s="10" t="n">
+      <c r="D26" s="7" t="n">
+        <v>-0.234331</v>
+      </c>
+      <c r="E26" s="12" t="n">
         <v>1.8196</v>
       </c>
       <c r="I26" s="8" t="n">
@@ -1131,7 +1370,18 @@
       <c r="J26" s="8" t="n">
         <v>0.042292</v>
       </c>
-      <c r="K26" s="9" t="inlineStr">
+      <c r="K26" s="9" t="n">
+        <v>672</v>
+      </c>
+      <c r="L26" s="9" t="n">
+        <v>7330</v>
+      </c>
+      <c r="M26" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N26" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1150,9 +1400,9 @@
         <v>-0.168284</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>-0.369092</v>
-      </c>
-      <c r="E27" s="10" t="n">
+        <v>-0.362099</v>
+      </c>
+      <c r="E27" s="12" t="n">
         <v>1.724</v>
       </c>
       <c r="I27" s="8" t="n">
@@ -1161,7 +1411,18 @@
       <c r="J27" s="8" t="n">
         <v>0.039306</v>
       </c>
-      <c r="K27" s="9" t="inlineStr">
+      <c r="K27" s="9" t="n">
+        <v>1668</v>
+      </c>
+      <c r="L27" s="9" t="n">
+        <v>8294</v>
+      </c>
+      <c r="M27" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N27" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1180,9 +1441,9 @@
         <v>-0.143149</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>-0.347641</v>
-      </c>
-      <c r="E28" s="10" t="n">
+        <v>-0.340648</v>
+      </c>
+      <c r="E28" s="12" t="n">
         <v>2.1422</v>
       </c>
       <c r="I28" s="8" t="n">
@@ -1191,7 +1452,18 @@
       <c r="J28" s="8" t="n">
         <v>0.042728</v>
       </c>
-      <c r="K28" s="9" t="inlineStr">
+      <c r="K28" s="9" t="n">
+        <v>1564</v>
+      </c>
+      <c r="L28" s="9" t="n">
+        <v>8870</v>
+      </c>
+      <c r="M28" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N28" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1210,9 +1482,9 @@
         <v>-0.153305</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>-0.248885</v>
-      </c>
-      <c r="E29" s="10" t="n">
+        <v>-0.241892</v>
+      </c>
+      <c r="E29" s="12" t="n">
         <v>1.9732</v>
       </c>
       <c r="I29" s="8" t="n">
@@ -1221,7 +1493,18 @@
       <c r="J29" s="8" t="n">
         <v>0.07223599999999999</v>
       </c>
-      <c r="K29" s="9" t="inlineStr">
+      <c r="K29" s="9" t="n">
+        <v>2835</v>
+      </c>
+      <c r="L29" s="9" t="n">
+        <v>12833</v>
+      </c>
+      <c r="M29" s="11" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="N29" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1240,9 +1523,9 @@
         <v>-0.139594</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>-0.23551</v>
-      </c>
-      <c r="E30" s="10" t="n">
+        <v>-0.228518</v>
+      </c>
+      <c r="E30" s="12" t="n">
         <v>2.2014</v>
       </c>
       <c r="I30" s="8" t="n">
@@ -1251,7 +1534,13 @@
       <c r="J30" s="8" t="n">
         <v>0.06432599999999999</v>
       </c>
-      <c r="K30" s="9" t="inlineStr">
+      <c r="K30" s="9" t="n">
+        <v>2951</v>
+      </c>
+      <c r="L30" s="9" t="n">
+        <v>12390</v>
+      </c>
+      <c r="N30" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1270,9 +1559,9 @@
         <v>-0.149017</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>-0.235507</v>
-      </c>
-      <c r="E31" s="10" t="n">
+        <v>-0.228514</v>
+      </c>
+      <c r="E31" s="12" t="n">
         <v>2.0446</v>
       </c>
       <c r="I31" s="8" t="n">
@@ -1281,7 +1570,13 @@
       <c r="J31" s="8" t="n">
         <v>0.07254099999999999</v>
       </c>
-      <c r="K31" s="9" t="inlineStr">
+      <c r="K31" s="9" t="n">
+        <v>2018</v>
+      </c>
+      <c r="L31" s="9" t="n">
+        <v>11235</v>
+      </c>
+      <c r="N31" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1300,9 +1595,9 @@
         <v>-0.142121</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>-0.28603</v>
-      </c>
-      <c r="E32" s="10" t="n">
+        <v>-0.279037</v>
+      </c>
+      <c r="E32" s="12" t="n">
         <v>2.1593</v>
       </c>
       <c r="I32" s="8" t="n">
@@ -1311,7 +1606,13 @@
       <c r="J32" s="8" t="n">
         <v>0.062436</v>
       </c>
-      <c r="K32" s="9" t="inlineStr">
+      <c r="K32" s="9" t="n">
+        <v>2501</v>
+      </c>
+      <c r="L32" s="9" t="n">
+        <v>13774</v>
+      </c>
+      <c r="N32" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1330,9 +1631,9 @@
         <v>-0.145641</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>-0.185896</v>
-      </c>
-      <c r="E33" s="10" t="n">
+        <v>-0.178903</v>
+      </c>
+      <c r="E33" s="12" t="n">
         <v>2.1007</v>
       </c>
       <c r="I33" s="8" t="n">
@@ -1341,7 +1642,13 @@
       <c r="J33" s="8" t="n">
         <v>0.083995</v>
       </c>
-      <c r="K33" s="9" t="inlineStr">
+      <c r="K33" s="9" t="n">
+        <v>2133</v>
+      </c>
+      <c r="L33" s="9" t="n">
+        <v>13346</v>
+      </c>
+      <c r="N33" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1360,9 +1667,9 @@
         <v>-0.144937</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>-0.144669</v>
-      </c>
-      <c r="E34" s="10" t="n">
+        <v>-0.137677</v>
+      </c>
+      <c r="E34" s="12" t="n">
         <v>2.1125</v>
       </c>
       <c r="I34" s="8" t="n">
@@ -1371,7 +1678,13 @@
       <c r="J34" s="8" t="n">
         <v>0.085355</v>
       </c>
-      <c r="K34" s="9" t="inlineStr">
+      <c r="K34" s="9" t="n">
+        <v>3490</v>
+      </c>
+      <c r="L34" s="9" t="n">
+        <v>20362</v>
+      </c>
+      <c r="N34" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1390,9 +1703,9 @@
         <v>-0.095984</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>-0.110158</v>
-      </c>
-      <c r="E35" s="10" t="n">
+        <v>-0.103165</v>
+      </c>
+      <c r="E35" s="12" t="n">
         <v>2.927</v>
       </c>
       <c r="I35" s="8" t="n">
@@ -1401,7 +1714,13 @@
       <c r="J35" s="8" t="n">
         <v>0.083896</v>
       </c>
-      <c r="K35" s="9" t="inlineStr">
+      <c r="K35" s="9" t="n">
+        <v>3223</v>
+      </c>
+      <c r="L35" s="9" t="n">
+        <v>15996</v>
+      </c>
+      <c r="N35" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1420,9 +1739,9 @@
         <v>-0.060465</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>-0.077393</v>
-      </c>
-      <c r="E36" s="10" t="n">
+        <v>-0.0704</v>
+      </c>
+      <c r="E36" s="12" t="n">
         <v>3.518</v>
       </c>
       <c r="I36" s="8" t="n">
@@ -1431,7 +1750,13 @@
       <c r="J36" s="8" t="n">
         <v>0.08376</v>
       </c>
-      <c r="K36" s="9" t="inlineStr">
+      <c r="K36" s="9" t="n">
+        <v>2636</v>
+      </c>
+      <c r="L36" s="9" t="n">
+        <v>16595</v>
+      </c>
+      <c r="N36" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1450,9 +1775,9 @@
         <v>0.012633</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>-0.10232</v>
-      </c>
-      <c r="E37" s="10" t="n">
+        <v>-0.095327</v>
+      </c>
+      <c r="E37" s="12" t="n">
         <v>4.7343</v>
       </c>
       <c r="I37" s="8" t="n">
@@ -1461,7 +1786,13 @@
       <c r="J37" s="8" t="n">
         <v>0.08457000000000001</v>
       </c>
-      <c r="K37" s="9" t="inlineStr">
+      <c r="K37" s="9" t="n">
+        <v>4526</v>
+      </c>
+      <c r="L37" s="9" t="n">
+        <v>19132</v>
+      </c>
+      <c r="N37" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1480,9 +1811,9 @@
         <v>0.039764</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>0.005979</v>
-      </c>
-      <c r="E38" s="10" t="n">
+        <v>0.012972</v>
+      </c>
+      <c r="E38" s="12" t="n">
         <v>5.1857</v>
       </c>
       <c r="I38" s="8" t="n">
@@ -1491,7 +1822,13 @@
       <c r="J38" s="8" t="n">
         <v>0.105222</v>
       </c>
-      <c r="K38" s="9" t="inlineStr">
+      <c r="K38" s="9" t="n">
+        <v>8018</v>
+      </c>
+      <c r="L38" s="9" t="n">
+        <v>25451</v>
+      </c>
+      <c r="N38" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1510,9 +1847,9 @@
         <v>0.075416</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>0.02131</v>
-      </c>
-      <c r="E39" s="10" t="n">
+        <v>0.028303</v>
+      </c>
+      <c r="E39" s="12" t="n">
         <v>5.7789</v>
       </c>
       <c r="I39" s="8" t="n">
@@ -1521,7 +1858,13 @@
       <c r="J39" s="8" t="n">
         <v>0.123064</v>
       </c>
-      <c r="K39" s="9" t="inlineStr">
+      <c r="K39" s="9" t="n">
+        <v>9369</v>
+      </c>
+      <c r="L39" s="9" t="n">
+        <v>24605</v>
+      </c>
+      <c r="N39" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1540,9 +1883,9 @@
         <v>0.07081</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>0.013822</v>
-      </c>
-      <c r="E40" s="10" t="n">
+        <v>0.020815</v>
+      </c>
+      <c r="E40" s="12" t="n">
         <v>5.7023</v>
       </c>
       <c r="I40" s="8" t="n">
@@ -1551,7 +1894,13 @@
       <c r="J40" s="8" t="n">
         <v>0.1189</v>
       </c>
-      <c r="K40" s="9" t="inlineStr">
+      <c r="K40" s="9" t="n">
+        <v>8420</v>
+      </c>
+      <c r="L40" s="9" t="n">
+        <v>24466</v>
+      </c>
+      <c r="N40" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1570,9 +1919,9 @@
         <v>0.11457</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>0.184042</v>
-      </c>
-      <c r="E41" s="10" t="n">
+        <v>0.191035</v>
+      </c>
+      <c r="E41" s="12" t="n">
         <v>6.4304</v>
       </c>
       <c r="I41" s="8" t="n">
@@ -1581,7 +1930,13 @@
       <c r="J41" s="8" t="n">
         <v>0.143258</v>
       </c>
-      <c r="K41" s="9" t="inlineStr">
+      <c r="K41" s="9" t="n">
+        <v>14390</v>
+      </c>
+      <c r="L41" s="9" t="n">
+        <v>36012</v>
+      </c>
+      <c r="N41" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1600,9 +1955,9 @@
         <v>0.108495</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>0.169019</v>
-      </c>
-      <c r="E42" s="10" t="n">
+        <v>0.176012</v>
+      </c>
+      <c r="E42" s="12" t="n">
         <v>6.3293</v>
       </c>
       <c r="I42" s="8" t="n">
@@ -1611,7 +1966,13 @@
       <c r="J42" s="8" t="n">
         <v>0.147607</v>
       </c>
-      <c r="K42" s="9" t="inlineStr">
+      <c r="K42" s="9" t="n">
+        <v>12738</v>
+      </c>
+      <c r="L42" s="9" t="n">
+        <v>30737</v>
+      </c>
+      <c r="N42" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1630,9 +1991,9 @@
         <v>0.129182</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>0.175043</v>
-      </c>
-      <c r="E43" s="10" t="n">
+        <v>0.182036</v>
+      </c>
+      <c r="E43" s="12" t="n">
         <v>6.6735</v>
       </c>
       <c r="I43" s="8" t="n">
@@ -1641,7 +2002,13 @@
       <c r="J43" s="8" t="n">
         <v>0.135935</v>
       </c>
-      <c r="K43" s="9" t="inlineStr">
+      <c r="K43" s="9" t="n">
+        <v>11676</v>
+      </c>
+      <c r="L43" s="9" t="n">
+        <v>30750</v>
+      </c>
+      <c r="N43" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1660,9 +2027,9 @@
         <v>0.176096</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>0.186241</v>
-      </c>
-      <c r="E44" s="10" t="n">
+        <v>0.193234</v>
+      </c>
+      <c r="E44" s="12" t="n">
         <v>7.4541</v>
       </c>
       <c r="I44" s="8" t="n">
@@ -1671,7 +2038,13 @@
       <c r="J44" s="8" t="n">
         <v>0.147817</v>
       </c>
-      <c r="K44" s="9" t="inlineStr">
+      <c r="K44" s="9" t="n">
+        <v>10050</v>
+      </c>
+      <c r="L44" s="9" t="n">
+        <v>37039</v>
+      </c>
+      <c r="N44" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1690,9 +2063,9 @@
         <v>0.24601</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>0.157927</v>
-      </c>
-      <c r="E45" s="10" t="n">
+        <v>0.164919</v>
+      </c>
+      <c r="E45" s="12" t="n">
         <v>8.6174</v>
       </c>
       <c r="I45" s="8" t="n">
@@ -1701,7 +2074,13 @@
       <c r="J45" s="8" t="n">
         <v>0.128426</v>
       </c>
-      <c r="K45" s="9" t="inlineStr">
+      <c r="K45" s="9" t="n">
+        <v>7153</v>
+      </c>
+      <c r="L45" s="9" t="n">
+        <v>31668</v>
+      </c>
+      <c r="N45" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1720,9 +2099,9 @@
         <v>0.255637</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>0.131868</v>
-      </c>
-      <c r="E46" s="10" t="n">
+        <v>0.13886</v>
+      </c>
+      <c r="E46" s="12" t="n">
         <v>8.7776</v>
       </c>
       <c r="I46" s="8" t="n">
@@ -1731,7 +2110,13 @@
       <c r="J46" s="8" t="n">
         <v>0.122308</v>
       </c>
-      <c r="K46" s="9" t="inlineStr">
+      <c r="K46" s="9" t="n">
+        <v>9302</v>
+      </c>
+      <c r="L46" s="9" t="n">
+        <v>33522</v>
+      </c>
+      <c r="N46" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1750,9 +2135,9 @@
         <v>0.288507</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>0.224133</v>
-      </c>
-      <c r="E47" s="10" t="n">
+        <v>0.231126</v>
+      </c>
+      <c r="E47" s="12" t="n">
         <v>9.3245</v>
       </c>
       <c r="I47" s="8" t="n">
@@ -1761,7 +2146,13 @@
       <c r="J47" s="8" t="n">
         <v>0.140499</v>
       </c>
-      <c r="K47" s="9" t="inlineStr">
+      <c r="K47" s="9" t="n">
+        <v>8118</v>
+      </c>
+      <c r="L47" s="9" t="n">
+        <v>34292</v>
+      </c>
+      <c r="N47" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1780,9 +2171,9 @@
         <v>0.285731</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>0.209719</v>
-      </c>
-      <c r="E48" s="10" t="n">
+        <v>0.216712</v>
+      </c>
+      <c r="E48" s="12" t="n">
         <v>9.2783</v>
       </c>
       <c r="I48" s="8" t="n">
@@ -1791,7 +2182,13 @@
       <c r="J48" s="8" t="n">
         <v>0.138715</v>
       </c>
-      <c r="K48" s="9" t="inlineStr">
+      <c r="K48" s="9" t="n">
+        <v>7117</v>
+      </c>
+      <c r="L48" s="9" t="n">
+        <v>29146</v>
+      </c>
+      <c r="N48" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1810,9 +2207,9 @@
         <v>0.256993</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>0.210833</v>
-      </c>
-      <c r="E49" s="10" t="n">
+        <v>0.217826</v>
+      </c>
+      <c r="E49" s="12" t="n">
         <v>8.8001</v>
       </c>
       <c r="I49" s="8" t="n">
@@ -1821,7 +2218,13 @@
       <c r="J49" s="8" t="n">
         <v>0.132361</v>
       </c>
-      <c r="K49" s="9" t="inlineStr">
+      <c r="K49" s="9" t="n">
+        <v>8061</v>
+      </c>
+      <c r="L49" s="9" t="n">
+        <v>31263</v>
+      </c>
+      <c r="N49" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1840,9 +2243,9 @@
         <v>0.256189</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>0.202951</v>
-      </c>
-      <c r="E50" s="10" t="n">
+        <v>0.209944</v>
+      </c>
+      <c r="E50" s="12" t="n">
         <v>8.786799999999999</v>
       </c>
       <c r="I50" s="8" t="n">
@@ -1851,7 +2254,13 @@
       <c r="J50" s="8" t="n">
         <v>0.13067</v>
       </c>
-      <c r="K50" s="9" t="inlineStr">
+      <c r="K50" s="9" t="n">
+        <v>7869</v>
+      </c>
+      <c r="L50" s="9" t="n">
+        <v>27688</v>
+      </c>
+      <c r="N50" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1870,9 +2279,9 @@
         <v>0.247624</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>0.172413</v>
-      </c>
-      <c r="E51" s="10" t="n">
+        <v>0.179406</v>
+      </c>
+      <c r="E51" s="12" t="n">
         <v>8.644299999999999</v>
       </c>
       <c r="I51" s="8" t="n">
@@ -1881,7 +2290,13 @@
       <c r="J51" s="8" t="n">
         <v>0.135901</v>
       </c>
-      <c r="K51" s="9" t="inlineStr">
+      <c r="K51" s="9" t="n">
+        <v>8996</v>
+      </c>
+      <c r="L51" s="9" t="n">
+        <v>27785</v>
+      </c>
+      <c r="N51" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1900,9 +2315,9 @@
         <v>0.247531</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>0.257608</v>
-      </c>
-      <c r="E52" s="10" t="n">
+        <v>0.264601</v>
+      </c>
+      <c r="E52" s="12" t="n">
         <v>8.6427</v>
       </c>
       <c r="I52" s="8" t="n">
@@ -1911,7 +2326,13 @@
       <c r="J52" s="8" t="n">
         <v>0.138861</v>
       </c>
-      <c r="K52" s="9" t="inlineStr">
+      <c r="K52" s="9" t="n">
+        <v>8641</v>
+      </c>
+      <c r="L52" s="9" t="n">
+        <v>28669</v>
+      </c>
+      <c r="N52" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1930,9 +2351,9 @@
         <v>0.242764</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>0.266172</v>
-      </c>
-      <c r="E53" s="10" t="n">
+        <v>0.273164</v>
+      </c>
+      <c r="E53" s="12" t="n">
         <v>8.5634</v>
       </c>
       <c r="I53" s="8" t="n">
@@ -1941,7 +2362,13 @@
       <c r="J53" s="8" t="n">
         <v>0.142346</v>
       </c>
-      <c r="K53" s="9" t="inlineStr">
+      <c r="K53" s="9" t="n">
+        <v>7707</v>
+      </c>
+      <c r="L53" s="9" t="n">
+        <v>24293</v>
+      </c>
+      <c r="N53" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1960,9 +2387,9 @@
         <v>0.260958</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>0.200402</v>
-      </c>
-      <c r="E54" s="10" t="n">
+        <v>0.207394</v>
+      </c>
+      <c r="E54" s="12" t="n">
         <v>8.866099999999999</v>
       </c>
       <c r="I54" s="8" t="n">
@@ -1971,7 +2398,13 @@
       <c r="J54" s="8" t="n">
         <v>0.129144</v>
       </c>
-      <c r="K54" s="9" t="inlineStr">
+      <c r="K54" s="9" t="n">
+        <v>7508</v>
+      </c>
+      <c r="L54" s="9" t="n">
+        <v>24043</v>
+      </c>
+      <c r="N54" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -1990,9 +2423,9 @@
         <v>0.268444</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>0.202264</v>
-      </c>
-      <c r="E55" s="10" t="n">
+        <v>0.209257</v>
+      </c>
+      <c r="E55" s="12" t="n">
         <v>8.9907</v>
       </c>
       <c r="I55" s="8" t="n">
@@ -2001,7 +2434,13 @@
       <c r="J55" s="8" t="n">
         <v>0.132003</v>
       </c>
-      <c r="K55" s="9" t="inlineStr">
+      <c r="K55" s="9" t="n">
+        <v>7731</v>
+      </c>
+      <c r="L55" s="9" t="n">
+        <v>25204</v>
+      </c>
+      <c r="N55" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2020,9 +2459,9 @@
         <v>0.24894</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="E56" s="10" t="n">
+        <v>0.141993</v>
+      </c>
+      <c r="E56" s="12" t="n">
         <v>8.6662</v>
       </c>
       <c r="I56" s="8" t="n">
@@ -2031,7 +2470,13 @@
       <c r="J56" s="8" t="n">
         <v>0.117318</v>
       </c>
-      <c r="K56" s="9" t="inlineStr">
+      <c r="K56" s="9" t="n">
+        <v>6747</v>
+      </c>
+      <c r="L56" s="9" t="n">
+        <v>25597</v>
+      </c>
+      <c r="N56" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2050,9 +2495,9 @@
         <v>0.211435</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>0.133073</v>
-      </c>
-      <c r="E57" s="10" t="n">
+        <v>0.140065</v>
+      </c>
+      <c r="E57" s="12" t="n">
         <v>8.0421</v>
       </c>
       <c r="I57" s="8" t="n">
@@ -2061,7 +2506,13 @@
       <c r="J57" s="8" t="n">
         <v>0.115488</v>
       </c>
-      <c r="K57" s="9" t="inlineStr">
+      <c r="K57" s="9" t="n">
+        <v>5942</v>
+      </c>
+      <c r="L57" s="9" t="n">
+        <v>26531</v>
+      </c>
+      <c r="N57" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2080,9 +2531,9 @@
         <v>0.208076</v>
       </c>
       <c r="D58" s="7" t="n">
-        <v>0.099829</v>
-      </c>
-      <c r="E58" s="10" t="n">
+        <v>0.106822</v>
+      </c>
+      <c r="E58" s="12" t="n">
         <v>7.9862</v>
       </c>
       <c r="I58" s="8" t="n">
@@ -2091,7 +2542,13 @@
       <c r="J58" s="8" t="n">
         <v>0.120869</v>
       </c>
-      <c r="K58" s="9" t="inlineStr">
+      <c r="K58" s="9" t="n">
+        <v>7417</v>
+      </c>
+      <c r="L58" s="9" t="n">
+        <v>23571</v>
+      </c>
+      <c r="N58" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2110,9 +2567,9 @@
         <v>0.13132</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>-0.029576</v>
-      </c>
-      <c r="E59" s="10" t="n">
+        <v>-0.022583</v>
+      </c>
+      <c r="E59" s="12" t="n">
         <v>6.7091</v>
       </c>
       <c r="I59" s="8" t="n">
@@ -2121,7 +2578,13 @@
       <c r="J59" s="8" t="n">
         <v>0.103097</v>
       </c>
-      <c r="K59" s="9" t="inlineStr">
+      <c r="K59" s="9" t="n">
+        <v>5236</v>
+      </c>
+      <c r="L59" s="9" t="n">
+        <v>17566</v>
+      </c>
+      <c r="N59" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2140,9 +2603,9 @@
         <v>0.08988400000000001</v>
       </c>
       <c r="D60" s="7" t="n">
-        <v>-0.08440599999999999</v>
-      </c>
-      <c r="E60" s="10" t="n">
+        <v>-0.077413</v>
+      </c>
+      <c r="E60" s="12" t="n">
         <v>6.0196</v>
       </c>
       <c r="I60" s="8" t="n">
@@ -2151,7 +2614,13 @@
       <c r="J60" s="8" t="n">
         <v>0.08440300000000001</v>
       </c>
-      <c r="K60" s="9" t="inlineStr">
+      <c r="K60" s="9" t="n">
+        <v>3361</v>
+      </c>
+      <c r="L60" s="9" t="n">
+        <v>14099</v>
+      </c>
+      <c r="N60" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2170,9 +2639,9 @@
         <v>0.075873</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>-0.04319</v>
-      </c>
-      <c r="E61" s="10" t="n">
+        <v>-0.036197</v>
+      </c>
+      <c r="E61" s="12" t="n">
         <v>5.7865</v>
       </c>
       <c r="I61" s="8" t="n">
@@ -2181,7 +2650,13 @@
       <c r="J61" s="8" t="n">
         <v>0.082458</v>
       </c>
-      <c r="K61" s="9" t="inlineStr">
+      <c r="K61" s="9" t="n">
+        <v>4277</v>
+      </c>
+      <c r="L61" s="9" t="n">
+        <v>16275</v>
+      </c>
+      <c r="N61" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2200,9 +2675,9 @@
         <v>0.044848</v>
       </c>
       <c r="D62" s="7" t="n">
-        <v>-0.101667</v>
-      </c>
-      <c r="E62" s="10" t="n">
+        <v>-0.094675</v>
+      </c>
+      <c r="E62" s="12" t="n">
         <v>5.2703</v>
       </c>
       <c r="I62" s="8" t="n">
@@ -2211,7 +2686,13 @@
       <c r="J62" s="8" t="n">
         <v>0.078038</v>
       </c>
-      <c r="K62" s="9" t="inlineStr">
+      <c r="K62" s="9" t="n">
+        <v>2877</v>
+      </c>
+      <c r="L62" s="9" t="n">
+        <v>13801</v>
+      </c>
+      <c r="N62" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2230,9 +2711,9 @@
         <v>-0.000402</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>-0.130819</v>
-      </c>
-      <c r="E63" s="10" t="n">
+        <v>-0.123826</v>
+      </c>
+      <c r="E63" s="12" t="n">
         <v>4.5174</v>
       </c>
       <c r="I63" s="8" t="n">
@@ -2241,7 +2722,13 @@
       <c r="J63" s="8" t="n">
         <v>0.073126</v>
       </c>
-      <c r="K63" s="9" t="inlineStr">
+      <c r="K63" s="9" t="n">
+        <v>2474</v>
+      </c>
+      <c r="L63" s="9" t="n">
+        <v>14304</v>
+      </c>
+      <c r="N63" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2260,9 +2747,9 @@
         <v>-0.044318</v>
       </c>
       <c r="D64" s="7" t="n">
-        <v>-0.103903</v>
-      </c>
-      <c r="E64" s="10" t="n">
+        <v>-0.09691</v>
+      </c>
+      <c r="E64" s="12" t="n">
         <v>3.7867</v>
       </c>
       <c r="I64" s="8" t="n">
@@ -2271,7 +2758,13 @@
       <c r="J64" s="8" t="n">
         <v>0.081695</v>
       </c>
-      <c r="K64" s="9" t="inlineStr">
+      <c r="K64" s="9" t="n">
+        <v>2866</v>
+      </c>
+      <c r="L64" s="9" t="n">
+        <v>15264</v>
+      </c>
+      <c r="N64" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2290,9 +2783,9 @@
         <v>-0.066895</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>-0.012276</v>
-      </c>
-      <c r="E65" s="10" t="n">
+        <v>-0.005283</v>
+      </c>
+      <c r="E65" s="12" t="n">
         <v>3.411</v>
       </c>
       <c r="I65" s="8" t="n">
@@ -2301,7 +2794,13 @@
       <c r="J65" s="8" t="n">
         <v>0.096706</v>
       </c>
-      <c r="K65" s="9" t="inlineStr">
+      <c r="K65" s="9" t="n">
+        <v>3376</v>
+      </c>
+      <c r="L65" s="9" t="n">
+        <v>15511</v>
+      </c>
+      <c r="N65" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2320,9 +2819,9 @@
         <v>-0.094778</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>-0.12511</v>
-      </c>
-      <c r="E66" s="10" t="n">
+        <v>-0.118118</v>
+      </c>
+      <c r="E66" s="12" t="n">
         <v>2.9471</v>
       </c>
       <c r="I66" s="8" t="n">
@@ -2331,7 +2830,13 @@
       <c r="J66" s="8" t="n">
         <v>0.08185000000000001</v>
       </c>
-      <c r="K66" s="9" t="inlineStr">
+      <c r="K66" s="9" t="n">
+        <v>4019</v>
+      </c>
+      <c r="L66" s="9" t="n">
+        <v>18534</v>
+      </c>
+      <c r="N66" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2350,9 +2855,9 @@
         <v>-0.095827</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>-0.148883</v>
-      </c>
-      <c r="E67" s="10" t="n">
+        <v>-0.14189</v>
+      </c>
+      <c r="E67" s="12" t="n">
         <v>2.9296</v>
       </c>
       <c r="I67" s="8" t="n">
@@ -2361,7 +2866,13 @@
       <c r="J67" s="8" t="n">
         <v>0.08667</v>
       </c>
-      <c r="K67" s="9" t="inlineStr">
+      <c r="K67" s="9" t="n">
+        <v>3916</v>
+      </c>
+      <c r="L67" s="9" t="n">
+        <v>18184</v>
+      </c>
+      <c r="N67" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2380,9 +2891,9 @@
         <v>-0.111136</v>
       </c>
       <c r="D68" s="7" t="n">
-        <v>-0.115637</v>
-      </c>
-      <c r="E68" s="10" t="n">
+        <v>-0.108644</v>
+      </c>
+      <c r="E68" s="12" t="n">
         <v>2.6749</v>
       </c>
       <c r="I68" s="8" t="n">
@@ -2391,7 +2902,13 @@
       <c r="J68" s="8" t="n">
         <v>0.07960100000000001</v>
       </c>
-      <c r="K68" s="9" t="inlineStr">
+      <c r="K68" s="9" t="n">
+        <v>3822</v>
+      </c>
+      <c r="L68" s="9" t="n">
+        <v>15138</v>
+      </c>
+      <c r="N68" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2410,9 +2927,9 @@
         <v>-0.145309</v>
       </c>
       <c r="D69" s="7" t="n">
-        <v>-0.128837</v>
-      </c>
-      <c r="E69" s="10" t="n">
+        <v>-0.121844</v>
+      </c>
+      <c r="E69" s="12" t="n">
         <v>2.1063</v>
       </c>
       <c r="I69" s="8" t="n">
@@ -2421,7 +2938,13 @@
       <c r="J69" s="8" t="n">
         <v>0.080369</v>
       </c>
-      <c r="K69" s="9" t="inlineStr">
+      <c r="K69" s="9" t="n">
+        <v>4496</v>
+      </c>
+      <c r="L69" s="9" t="n">
+        <v>20605</v>
+      </c>
+      <c r="N69" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2440,9 +2963,9 @@
         <v>-0.172221</v>
       </c>
       <c r="D70" s="7" t="n">
-        <v>-0.137364</v>
-      </c>
-      <c r="E70" s="10" t="n">
+        <v>-0.130371</v>
+      </c>
+      <c r="E70" s="12" t="n">
         <v>1.6585</v>
       </c>
       <c r="I70" s="8" t="n">
@@ -2451,7 +2974,13 @@
       <c r="J70" s="8" t="n">
         <v>0.075582</v>
       </c>
-      <c r="K70" s="9" t="inlineStr">
+      <c r="K70" s="9" t="n">
+        <v>3617</v>
+      </c>
+      <c r="L70" s="9" t="n">
+        <v>18417</v>
+      </c>
+      <c r="N70" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2470,9 +2999,9 @@
         <v>-0.158326</v>
       </c>
       <c r="D71" s="7" t="n">
-        <v>-0.103087</v>
-      </c>
-      <c r="E71" s="10" t="n">
+        <v>-0.096095</v>
+      </c>
+      <c r="E71" s="12" t="n">
         <v>1.8897</v>
       </c>
       <c r="I71" s="8" t="n">
@@ -2481,7 +3010,13 @@
       <c r="J71" s="8" t="n">
         <v>0.076083</v>
       </c>
-      <c r="K71" s="9" t="inlineStr">
+      <c r="K71" s="9" t="n">
+        <v>2897</v>
+      </c>
+      <c r="L71" s="9" t="n">
+        <v>17770</v>
+      </c>
+      <c r="N71" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2500,9 +3035,9 @@
         <v>-0.165385</v>
       </c>
       <c r="D72" s="7" t="n">
-        <v>-0.162352</v>
-      </c>
-      <c r="E72" s="10" t="n">
+        <v>-0.155359</v>
+      </c>
+      <c r="E72" s="12" t="n">
         <v>1.7722</v>
       </c>
       <c r="I72" s="8" t="n">
@@ -2511,7 +3046,13 @@
       <c r="J72" s="8" t="n">
         <v>0.08258799999999999</v>
       </c>
-      <c r="K72" s="9" t="inlineStr">
+      <c r="K72" s="9" t="n">
+        <v>3862</v>
+      </c>
+      <c r="L72" s="9" t="n">
+        <v>20451</v>
+      </c>
+      <c r="N72" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2530,9 +3071,9 @@
         <v>-0.170796</v>
       </c>
       <c r="D73" s="7" t="n">
-        <v>-0.181021</v>
-      </c>
-      <c r="E73" s="10" t="n">
+        <v>-0.174029</v>
+      </c>
+      <c r="E73" s="12" t="n">
         <v>1.6822</v>
       </c>
       <c r="I73" s="8" t="n">
@@ -2541,7 +3082,13 @@
       <c r="J73" s="8" t="n">
         <v>0.077455</v>
       </c>
-      <c r="K73" s="9" t="inlineStr">
+      <c r="K73" s="9" t="n">
+        <v>3605</v>
+      </c>
+      <c r="L73" s="9" t="n">
+        <v>18669</v>
+      </c>
+      <c r="N73" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2560,9 +3107,9 @@
         <v>-0.18234</v>
       </c>
       <c r="D74" s="7" t="n">
-        <v>-0.149287</v>
-      </c>
-      <c r="E74" s="10" t="n">
+        <v>-0.142294</v>
+      </c>
+      <c r="E74" s="12" t="n">
         <v>1.4901</v>
       </c>
       <c r="I74" s="8" t="n">
@@ -2571,7 +3118,13 @@
       <c r="J74" s="8" t="n">
         <v>0.08115700000000001</v>
       </c>
-      <c r="K74" s="9" t="inlineStr">
+      <c r="K74" s="9" t="n">
+        <v>4229</v>
+      </c>
+      <c r="L74" s="9" t="n">
+        <v>22204</v>
+      </c>
+      <c r="N74" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2590,9 +3143,9 @@
         <v>-0.168029</v>
       </c>
       <c r="D75" s="7" t="n">
-        <v>-0.031121</v>
-      </c>
-      <c r="E75" s="10" t="n">
+        <v>-0.024129</v>
+      </c>
+      <c r="E75" s="12" t="n">
         <v>1.7282</v>
       </c>
       <c r="I75" s="8" t="n">
@@ -2601,7 +3154,13 @@
       <c r="J75" s="8" t="n">
         <v>0.089045</v>
       </c>
-      <c r="K75" s="9" t="inlineStr">
+      <c r="K75" s="9" t="n">
+        <v>4272</v>
+      </c>
+      <c r="L75" s="9" t="n">
+        <v>23505</v>
+      </c>
+      <c r="N75" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2620,9 +3179,9 @@
         <v>-0.148303</v>
       </c>
       <c r="D76" s="7" t="n">
-        <v>-0.06400400000000001</v>
-      </c>
-      <c r="E76" s="10" t="n">
+        <v>-0.057012</v>
+      </c>
+      <c r="E76" s="12" t="n">
         <v>2.0565</v>
       </c>
       <c r="I76" s="8" t="n">
@@ -2631,7 +3190,13 @@
       <c r="J76" s="8" t="n">
         <v>0.094443</v>
       </c>
-      <c r="K76" s="9" t="inlineStr">
+      <c r="K76" s="9" t="n">
+        <v>2813</v>
+      </c>
+      <c r="L76" s="9" t="n">
+        <v>23538</v>
+      </c>
+      <c r="N76" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2650,9 +3215,9 @@
         <v>-0.157881</v>
       </c>
       <c r="D77" s="7" t="n">
-        <v>-0.06710099999999999</v>
-      </c>
-      <c r="E77" s="10" t="n">
+        <v>-0.060108</v>
+      </c>
+      <c r="E77" s="12" t="n">
         <v>1.8971</v>
       </c>
       <c r="I77" s="8" t="n">
@@ -2661,7 +3226,13 @@
       <c r="J77" s="8" t="n">
         <v>0.098329</v>
       </c>
-      <c r="K77" s="9" t="inlineStr">
+      <c r="K77" s="9" t="n">
+        <v>2474</v>
+      </c>
+      <c r="L77" s="9" t="n">
+        <v>21011</v>
+      </c>
+      <c r="N77" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2680,9 +3251,9 @@
         <v>-0.163712</v>
       </c>
       <c r="D78" s="7" t="n">
-        <v>-0.127624</v>
-      </c>
-      <c r="E78" s="10" t="n">
+        <v>-0.120631</v>
+      </c>
+      <c r="E78" s="12" t="n">
         <v>1.8001</v>
       </c>
       <c r="I78" s="8" t="n">
@@ -2691,7 +3262,13 @@
       <c r="J78" s="8" t="n">
         <v>0.076053</v>
       </c>
-      <c r="K78" s="9" t="inlineStr">
+      <c r="K78" s="9" t="n">
+        <v>3152</v>
+      </c>
+      <c r="L78" s="9" t="n">
+        <v>24312</v>
+      </c>
+      <c r="N78" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2710,9 +3287,9 @@
         <v>-0.181319</v>
       </c>
       <c r="D79" s="7" t="n">
-        <v>-0.14477</v>
-      </c>
-      <c r="E79" s="10" t="n">
+        <v>-0.137777</v>
+      </c>
+      <c r="E79" s="12" t="n">
         <v>1.5071</v>
       </c>
       <c r="I79" s="8" t="n">
@@ -2721,7 +3298,13 @@
       <c r="J79" s="8" t="n">
         <v>0.077835</v>
       </c>
-      <c r="K79" s="9" t="inlineStr">
+      <c r="K79" s="9" t="n">
+        <v>2702</v>
+      </c>
+      <c r="L79" s="9" t="n">
+        <v>20916</v>
+      </c>
+      <c r="N79" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2740,9 +3323,9 @@
         <v>-0.192353</v>
       </c>
       <c r="D80" s="7" t="n">
-        <v>-0.092352</v>
-      </c>
-      <c r="E80" s="10" t="n">
+        <v>-0.085359</v>
+      </c>
+      <c r="E80" s="12" t="n">
         <v>1.3235</v>
       </c>
       <c r="I80" s="8" t="n">
@@ -2751,7 +3334,13 @@
       <c r="J80" s="8" t="n">
         <v>0.08944000000000001</v>
       </c>
-      <c r="K80" s="9" t="inlineStr">
+      <c r="K80" s="9" t="n">
+        <v>2482</v>
+      </c>
+      <c r="L80" s="9" t="n">
+        <v>25559</v>
+      </c>
+      <c r="N80" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2770,9 +3359,9 @@
         <v>-0.173382</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>-0.11655</v>
-      </c>
-      <c r="E81" s="10" t="n">
+        <v>-0.109557</v>
+      </c>
+      <c r="E81" s="12" t="n">
         <v>1.6392</v>
       </c>
       <c r="I81" s="8" t="n">
@@ -2781,7 +3370,13 @@
       <c r="J81" s="8" t="n">
         <v>0.090432</v>
       </c>
-      <c r="K81" s="9" t="inlineStr">
+      <c r="K81" s="9" t="n">
+        <v>2228</v>
+      </c>
+      <c r="L81" s="9" t="n">
+        <v>26130</v>
+      </c>
+      <c r="N81" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2800,9 +3395,9 @@
         <v>-0.16876</v>
       </c>
       <c r="D82" s="7" t="n">
-        <v>-0.087672</v>
-      </c>
-      <c r="E82" s="10" t="n">
+        <v>-0.080679</v>
+      </c>
+      <c r="E82" s="12" t="n">
         <v>1.7161</v>
       </c>
       <c r="I82" s="8" t="n">
@@ -2811,7 +3406,13 @@
       <c r="J82" s="8" t="n">
         <v>0.097691</v>
       </c>
-      <c r="K82" s="9" t="inlineStr">
+      <c r="K82" s="9" t="n">
+        <v>2238</v>
+      </c>
+      <c r="L82" s="9" t="n">
+        <v>22827</v>
+      </c>
+      <c r="N82" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2830,9 +3431,9 @@
         <v>-0.169874</v>
       </c>
       <c r="D83" s="7" t="n">
-        <v>-0.140612</v>
-      </c>
-      <c r="E83" s="10" t="n">
+        <v>-0.133619</v>
+      </c>
+      <c r="E83" s="12" t="n">
         <v>1.6975</v>
       </c>
       <c r="I83" s="8" t="n">
@@ -2841,7 +3442,13 @@
       <c r="J83" s="8" t="n">
         <v>0.099616</v>
       </c>
-      <c r="K83" s="9" t="inlineStr">
+      <c r="K83" s="9" t="n">
+        <v>2259</v>
+      </c>
+      <c r="L83" s="9" t="n">
+        <v>23972</v>
+      </c>
+      <c r="N83" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2859,10 +3466,10 @@
       <c r="C84" s="7" t="n">
         <v>-0.169702</v>
       </c>
-      <c r="E84" s="10" t="n">
+      <c r="E84" s="12" t="n">
         <v>1.7004</v>
       </c>
-      <c r="K84" s="9" t="inlineStr">
+      <c r="N84" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2880,10 +3487,10 @@
       <c r="C85" s="7" t="n">
         <v>-0.206344</v>
       </c>
-      <c r="E85" s="10" t="n">
+      <c r="E85" s="12" t="n">
         <v>1.0907</v>
       </c>
-      <c r="K85" s="9" t="inlineStr">
+      <c r="N85" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2901,10 +3508,10 @@
       <c r="C86" s="7" t="n">
         <v>-0.198116</v>
       </c>
-      <c r="E86" s="10" t="n">
+      <c r="E86" s="12" t="n">
         <v>1.2276</v>
       </c>
-      <c r="K86" s="9" t="inlineStr">
+      <c r="N86" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2922,10 +3529,10 @@
       <c r="C87" s="7" t="n">
         <v>-0.202026</v>
       </c>
-      <c r="E87" s="10" t="n">
+      <c r="E87" s="12" t="n">
         <v>1.1626</v>
       </c>
-      <c r="K87" s="9" t="inlineStr">
+      <c r="N87" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2943,10 +3550,10 @@
       <c r="C88" s="7" t="n">
         <v>-0.199292</v>
       </c>
-      <c r="E88" s="10" t="n">
+      <c r="E88" s="12" t="n">
         <v>1.208</v>
       </c>
-      <c r="K88" s="9" t="inlineStr">
+      <c r="N88" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2964,10 +3571,10 @@
       <c r="C89" s="7" t="n">
         <v>-0.193175</v>
       </c>
-      <c r="E89" s="10" t="n">
+      <c r="E89" s="12" t="n">
         <v>1.3098</v>
       </c>
-      <c r="K89" s="9" t="inlineStr">
+      <c r="N89" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -2985,10 +3592,10 @@
       <c r="C90" s="7" t="n">
         <v>-0.182209</v>
       </c>
-      <c r="E90" s="10" t="n">
+      <c r="E90" s="12" t="n">
         <v>1.4923</v>
       </c>
-      <c r="K90" s="9" t="inlineStr">
+      <c r="N90" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -3006,10 +3613,10 @@
       <c r="C91" s="7" t="n">
         <v>-0.119454</v>
       </c>
-      <c r="E91" s="10" t="n">
+      <c r="E91" s="12" t="n">
         <v>2.5365</v>
       </c>
-      <c r="K91" s="9" t="inlineStr">
+      <c r="N91" s="10" t="inlineStr">
         <is>
           <t>despeje 2026Q1</t>
         </is>
@@ -3027,10 +3634,10 @@
       <c r="C92" s="7" t="n">
         <v>-0.048851</v>
       </c>
-      <c r="E92" s="10" t="n">
+      <c r="E92" s="12" t="n">
         <v>3.7112</v>
       </c>
-      <c r="K92" s="9" t="inlineStr">
+      <c r="N92" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -3048,10 +3655,10 @@
       <c r="C93" s="7" t="n">
         <v>-0.035404</v>
       </c>
-      <c r="E93" s="10" t="n">
+      <c r="E93" s="12" t="n">
         <v>3.935</v>
       </c>
-      <c r="K93" s="9" t="inlineStr">
+      <c r="N93" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -3069,19 +3676,19 @@
       <c r="C94" s="7" t="n">
         <v>-0.042183</v>
       </c>
-      <c r="E94" s="10" t="n">
+      <c r="E94" s="12" t="n">
         <v>3.8222</v>
       </c>
-      <c r="F94" s="10" t="n">
+      <c r="F94" s="12" t="n">
         <v>3.8222</v>
       </c>
-      <c r="G94" s="10" t="n">
+      <c r="G94" s="12" t="n">
         <v>3.8222</v>
       </c>
-      <c r="H94" s="10" t="n">
+      <c r="H94" s="12" t="n">
         <v>3.8222</v>
       </c>
-      <c r="K94" s="9" t="inlineStr">
+      <c r="N94" s="10" t="inlineStr">
         <is>
           <t>observado</t>
         </is>
@@ -3099,16 +3706,16 @@
       <c r="C95" s="7" t="n">
         <v>-0.031451</v>
       </c>
-      <c r="F95" s="10" t="n">
+      <c r="F95" s="12" t="n">
         <v>4.0008</v>
       </c>
-      <c r="G95" s="10" t="n">
+      <c r="G95" s="12" t="n">
         <v>3.9579</v>
       </c>
-      <c r="H95" s="10" t="n">
+      <c r="H95" s="12" t="n">
         <v>4.0118</v>
       </c>
-      <c r="K95" s="9" t="inlineStr">
+      <c r="N95" s="10" t="inlineStr">
         <is>
           <t>proy BASE</t>
         </is>
@@ -3126,16 +3733,16 @@
       <c r="C96" s="7" t="n">
         <v>-0.023505</v>
       </c>
-      <c r="F96" s="10" t="n">
+      <c r="F96" s="12" t="n">
         <v>4.133</v>
       </c>
-      <c r="G96" s="10" t="n">
+      <c r="G96" s="12" t="n">
         <v>4.0518</v>
       </c>
-      <c r="H96" s="10" t="n">
+      <c r="H96" s="12" t="n">
         <v>4.1542</v>
       </c>
-      <c r="K96" s="9" t="inlineStr">
+      <c r="N96" s="10" t="inlineStr">
         <is>
           <t>proy BASE</t>
         </is>
@@ -3153,16 +3760,16 @@
       <c r="C97" s="7" t="n">
         <v>-0.016471</v>
       </c>
-      <c r="F97" s="10" t="n">
+      <c r="F97" s="12" t="n">
         <v>4.25</v>
       </c>
-      <c r="G97" s="10" t="n">
+      <c r="G97" s="12" t="n">
         <v>4.14</v>
       </c>
-      <c r="H97" s="10" t="n">
+      <c r="H97" s="12" t="n">
         <v>4.3</v>
       </c>
-      <c r="K97" s="9" t="inlineStr">
+      <c r="N97" s="10" t="inlineStr">
         <is>
           <t>proy BASE</t>
         </is>
@@ -3180,16 +3787,16 @@
       <c r="C98" s="7" t="n">
         <v>-0.00844</v>
       </c>
-      <c r="F98" s="10" t="n">
+      <c r="F98" s="12" t="n">
         <v>4.3836</v>
       </c>
-      <c r="G98" s="10" t="n">
+      <c r="G98" s="12" t="n">
         <v>4.2533</v>
       </c>
-      <c r="H98" s="10" t="n">
+      <c r="H98" s="12" t="n">
         <v>4.4974</v>
       </c>
-      <c r="K98" s="9" t="inlineStr">
+      <c r="N98" s="10" t="inlineStr">
         <is>
           <t>proy BASE</t>
         </is>
@@ -3207,16 +3814,16 @@
       <c r="C99" s="7" t="n">
         <v>-0.00107</v>
       </c>
-      <c r="F99" s="10" t="n">
+      <c r="F99" s="12" t="n">
         <v>4.5063</v>
       </c>
-      <c r="G99" s="10" t="n">
+      <c r="G99" s="12" t="n">
         <v>4.3616</v>
       </c>
-      <c r="H99" s="10" t="n">
+      <c r="H99" s="12" t="n">
         <v>4.6984</v>
       </c>
-      <c r="K99" s="9" t="inlineStr">
+      <c r="N99" s="10" t="inlineStr">
         <is>
           <t>proy BASE</t>
         </is>
@@ -3234,16 +3841,16 @@
       <c r="C100" s="7" t="n">
         <v>0.00216</v>
       </c>
-      <c r="F100" s="10" t="n">
+      <c r="F100" s="12" t="n">
         <v>4.56</v>
       </c>
-      <c r="G100" s="10" t="n">
+      <c r="G100" s="12" t="n">
         <v>4.41</v>
       </c>
-      <c r="H100" s="10" t="n">
+      <c r="H100" s="12" t="n">
         <v>4.81</v>
       </c>
-      <c r="K100" s="9" t="inlineStr">
+      <c r="N100" s="10" t="inlineStr">
         <is>
           <t>proy BASE</t>
         </is>
@@ -3261,16 +3868,16 @@
       <c r="C101" s="7" t="n">
         <v>0.001191</v>
       </c>
-      <c r="F101" s="10" t="n">
+      <c r="F101" s="12" t="n">
         <v>4.5439</v>
       </c>
-      <c r="G101" s="10" t="n">
+      <c r="G101" s="12" t="n">
         <v>4.4035</v>
       </c>
-      <c r="H101" s="10" t="n">
+      <c r="H101" s="12" t="n">
         <v>4.8415</v>
       </c>
-      <c r="K101" s="9" t="inlineStr">
+      <c r="N101" s="10" t="inlineStr">
         <is>
           <t>proy BASE</t>
         </is>
@@ -3288,16 +3895,16 @@
       <c r="C102" s="7" t="n">
         <v>-0.001247</v>
       </c>
-      <c r="F102" s="10" t="n">
+      <c r="F102" s="12" t="n">
         <v>4.5033</v>
       </c>
-      <c r="G102" s="10" t="n">
+      <c r="G102" s="12" t="n">
         <v>4.3858</v>
       </c>
-      <c r="H102" s="10" t="n">
+      <c r="H102" s="12" t="n">
         <v>4.8624</v>
       </c>
-      <c r="K102" s="9" t="inlineStr">
+      <c r="N102" s="10" t="inlineStr">
         <is>
           <t>proy BASE</t>
         </is>
@@ -3315,16 +3922,16 @@
       <c r="C103" s="7" t="n">
         <v>-0.004451</v>
       </c>
-      <c r="F103" s="10" t="n">
+      <c r="F103" s="12" t="n">
         <v>4.45</v>
       </c>
-      <c r="G103" s="10" t="n">
+      <c r="G103" s="12" t="n">
         <v>4.36</v>
       </c>
-      <c r="H103" s="10" t="n">
+      <c r="H103" s="12" t="n">
         <v>4.87</v>
       </c>
-      <c r="K103" s="9" t="inlineStr">
+      <c r="N103" s="10" t="inlineStr">
         <is>
           <t>proy BASE</t>
         </is>
@@ -3342,16 +3949,16 @@
       <c r="C104" s="7" t="n">
         <v>-0.009642</v>
       </c>
-      <c r="F104" s="10" t="n">
+      <c r="F104" s="12" t="n">
         <v>4.3636</v>
       </c>
-      <c r="G104" s="10" t="n">
+      <c r="G104" s="12" t="n">
         <v>4.289</v>
       </c>
-      <c r="H104" s="10" t="n">
+      <c r="H104" s="12" t="n">
         <v>4.8074</v>
       </c>
-      <c r="K104" s="9" t="inlineStr">
+      <c r="N104" s="10" t="inlineStr">
         <is>
           <t>proy BASE</t>
         </is>
@@ -3369,16 +3976,16 @@
       <c r="C105" s="7" t="n">
         <v>-0.017272</v>
       </c>
-      <c r="F105" s="10" t="n">
+      <c r="F105" s="12" t="n">
         <v>4.2367</v>
       </c>
-      <c r="G105" s="10" t="n">
+      <c r="G105" s="12" t="n">
         <v>4.1639</v>
       </c>
-      <c r="H105" s="10" t="n">
+      <c r="H105" s="12" t="n">
         <v>4.6648</v>
       </c>
-      <c r="K105" s="9" t="inlineStr">
+      <c r="N105" s="10" t="inlineStr">
         <is>
           <t>proy BASE</t>
         </is>
@@ -3396,16 +4003,16 @@
       <c r="C106" s="7" t="n">
         <v>-0.025486</v>
       </c>
-      <c r="F106" s="10" t="n">
+      <c r="F106" s="12" t="n">
         <v>4.1</v>
       </c>
-      <c r="G106" s="10" t="n">
+      <c r="G106" s="12" t="n">
         <v>4.03</v>
       </c>
-      <c r="H106" s="10" t="n">
+      <c r="H106" s="12" t="n">
         <v>4.51</v>
       </c>
-      <c r="K106" s="9" t="inlineStr">
+      <c r="N106" s="10" t="inlineStr">
         <is>
           <t>proy BASE</t>
         </is>
@@ -3423,16 +4030,16 @@
       <c r="C107" s="7" t="n">
         <v>-0.034118</v>
       </c>
-      <c r="F107" s="10" t="n">
+      <c r="F107" s="12" t="n">
         <v>3.9564</v>
       </c>
-      <c r="G107" s="10" t="n">
+      <c r="G107" s="12" t="n">
         <v>3.8955</v>
       </c>
-      <c r="H107" s="10" t="n">
+      <c r="H107" s="12" t="n">
         <v>4.3562</v>
       </c>
-      <c r="K107" s="9" t="inlineStr">
+      <c r="N107" s="10" t="inlineStr">
         <is>
           <t>proy BASE</t>
         </is>
@@ -3450,16 +4057,16 @@
       <c r="C108" s="7" t="n">
         <v>-0.043501</v>
       </c>
-      <c r="F108" s="10" t="n">
+      <c r="F108" s="12" t="n">
         <v>3.8002</v>
       </c>
-      <c r="G108" s="10" t="n">
+      <c r="G108" s="12" t="n">
         <v>3.7498</v>
       </c>
-      <c r="H108" s="10" t="n">
+      <c r="H108" s="12" t="n">
         <v>4.1858</v>
       </c>
-      <c r="K108" s="9" t="inlineStr">
+      <c r="N108" s="10" t="inlineStr">
         <is>
           <t>proy BASE</t>
         </is>
@@ -3477,16 +4084,16 @@
       <c r="C109" s="7" t="n">
         <v>-0.052531</v>
       </c>
-      <c r="F109" s="10" t="n">
+      <c r="F109" s="12" t="n">
         <v>3.65</v>
       </c>
-      <c r="G109" s="10" t="n">
+      <c r="G109" s="12" t="n">
         <v>3.61</v>
       </c>
-      <c r="H109" s="10" t="n">
+      <c r="H109" s="12" t="n">
         <v>4.02</v>
       </c>
-      <c r="K109" s="9" t="inlineStr">
+      <c r="N109" s="10" t="inlineStr">
         <is>
           <t>proy BASE</t>
         </is>
@@ -3504,16 +4111,16 @@
       <c r="C110" s="7" t="n">
         <v>-0.060556</v>
       </c>
-      <c r="F110" s="10" t="n">
+      <c r="F110" s="12" t="n">
         <v>3.5165</v>
       </c>
-      <c r="G110" s="10" t="n">
+      <c r="G110" s="12" t="n">
         <v>3.487</v>
       </c>
-      <c r="H110" s="10" t="n">
+      <c r="H110" s="12" t="n">
         <v>3.8699</v>
       </c>
-      <c r="K110" s="9" t="inlineStr">
+      <c r="N110" s="10" t="inlineStr">
         <is>
           <t>proy BASE</t>
         </is>
@@ -3531,16 +4138,16 @@
       <c r="C111" s="7" t="n">
         <v>-0.06826699999999999</v>
       </c>
-      <c r="F111" s="10" t="n">
+      <c r="F111" s="12" t="n">
         <v>3.3882</v>
       </c>
-      <c r="G111" s="10" t="n">
+      <c r="G111" s="12" t="n">
         <v>3.3692</v>
       </c>
-      <c r="H111" s="10" t="n">
+      <c r="H111" s="12" t="n">
         <v>3.724</v>
       </c>
-      <c r="K111" s="9" t="inlineStr">
+      <c r="N111" s="10" t="inlineStr">
         <is>
           <t>proy BASE</t>
         </is>
@@ -3558,16 +4165,16 @@
       <c r="C112" s="7" t="n">
         <v>-0.076571</v>
       </c>
-      <c r="F112" s="10" t="n">
+      <c r="F112" s="12" t="n">
         <v>3.25</v>
       </c>
-      <c r="G112" s="10" t="n">
+      <c r="G112" s="12" t="n">
         <v>3.24</v>
       </c>
-      <c r="H112" s="10" t="n">
+      <c r="H112" s="12" t="n">
         <v>3.57</v>
       </c>
-      <c r="K112" s="9" t="inlineStr">
+      <c r="N112" s="10" t="inlineStr">
         <is>
           <t>proy BASE</t>
         </is>
@@ -3585,167 +4192,218 @@
       <c r="C113" s="7" t="n">
         <v>-0.086835</v>
       </c>
-      <c r="F113" s="10" t="n">
+      <c r="F113" s="12" t="n">
         <v>3.0792</v>
       </c>
-      <c r="G113" s="10" t="n">
+      <c r="G113" s="12" t="n">
         <v>3.075</v>
       </c>
-      <c r="H113" s="10" t="n">
+      <c r="H113" s="12" t="n">
         <v>3.387</v>
       </c>
-      <c r="K113" s="9" t="inlineStr">
+      <c r="N113" s="10" t="inlineStr">
         <is>
           <t>proy BASE</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="11" t="inlineStr">
+      <c r="A116" s="14" t="inlineStr">
         <is>
           <t>Parametros y fronteras</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="12" t="inlineStr">
+      <c r="A117" s="15" t="inlineStr">
         <is>
           <t>beta</t>
         </is>
       </c>
-      <c r="B117" s="13" t="inlineStr">
+      <c r="B117" s="16" t="inlineStr">
         <is>
           <t>0.0601</t>
         </is>
       </c>
-      <c r="C117" s="14" t="inlineStr">
+      <c r="C117" s="17" t="inlineStr">
         <is>
           <t>lleva la inflacion a unidades de ciclo</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="12" t="inlineStr">
+      <c r="A118" s="15" t="inlineStr">
         <is>
           <t>mu</t>
         </is>
       </c>
-      <c r="B118" s="13" t="inlineStr">
+      <c r="B118" s="16" t="inlineStr">
         <is>
           <t>4.5241</t>
         </is>
       </c>
-      <c r="C118" s="14" t="inlineStr">
+      <c r="C118" s="17" t="inlineStr">
         <is>
           <t>inflacion media; con infl = mu el ciclo vale 0</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="12" t="inlineStr">
+      <c r="A119" s="15" t="inlineStr">
         <is>
           <t>carga</t>
         </is>
       </c>
-      <c r="B119" s="13" t="inlineStr">
+      <c r="B119" s="16" t="inlineStr">
         <is>
           <t>+0.7284</t>
         </is>
       </c>
-      <c r="C119" s="14" t="inlineStr">
+      <c r="C119" s="17" t="inlineStr">
         <is>
           <t>lleva el ciclo al probit de la mora</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="12" t="inlineStr">
+      <c r="A120" s="15" t="inlineStr">
         <is>
           <t>rho</t>
         </is>
       </c>
-      <c r="B120" s="13" t="inlineStr">
+      <c r="B120" s="16" t="inlineStr">
         <is>
           <t>0.0332</t>
         </is>
       </c>
-      <c r="C120" s="14" t="inlineStr">
+      <c r="C120" s="17" t="inlineStr">
         <is>
           <t>correlacion de activos (piso; el panel midio 0.0244)</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="12" t="inlineStr">
+      <c r="A121" s="15" t="inlineStr">
         <is>
           <t>lambda</t>
         </is>
       </c>
-      <c r="B121" s="13" t="inlineStr">
+      <c r="B121" s="16" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="C121" s="14" t="inlineStr">
+      <c r="C121" s="17" t="inlineStr">
         <is>
           <t>sensibilidad (tope: el MLE pide 2.60)</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="15" t="inlineStr"/>
-      <c r="B122" s="13" t="inlineStr"/>
-      <c r="C122" s="14" t="inlineStr"/>
+      <c r="A122" s="18" t="inlineStr"/>
+      <c r="B122" s="16" t="inlineStr"/>
+      <c r="C122" s="17" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="12" t="inlineStr">
+      <c r="A123" s="15" t="inlineStr">
         <is>
           <t>RD hasta</t>
         </is>
       </c>
-      <c r="B123" s="13" t="inlineStr">
+      <c r="B123" s="16" t="inlineStr">
         <is>
           <t>202506</t>
         </is>
       </c>
-      <c r="C123" s="14" t="inlineStr">
+      <c r="C123" s="17" t="inlineStr">
         <is>
           <t>el target necesita 12 meses de maduracion</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="12" t="inlineStr">
+      <c r="A124" s="15" t="inlineStr">
+        <is>
+          <t>Meses COVID</t>
+        </is>
+      </c>
+      <c r="B124" s="16" t="inlineStr">
+        <is>
+          <t>2020 completo</t>
+        </is>
+      </c>
+      <c r="C124" s="17" t="inlineStr">
+        <is>
+          <t>el pipeline los excluye de LRA y rho; aca van marcados</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="15" t="inlineStr">
+        <is>
+          <t>r ciclo~inflacion</t>
+        </is>
+      </c>
+      <c r="B125" s="16" t="inlineStr">
+        <is>
+          <t>+0.90</t>
+        </is>
+      </c>
+      <c r="C125" s="17" t="inlineStr">
+        <is>
+          <t>excluyendo 2020, que es el criterio del pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   sin excluir nada</t>
+        </is>
+      </c>
+      <c r="B126" s="16" t="inlineStr">
+        <is>
+          <t>+0.80</t>
+        </is>
+      </c>
+      <c r="C126" s="17" t="inlineStr">
+        <is>
+          <t>en el confinamiento mora e inflacion se desacoplan</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="15" t="inlineStr">
         <is>
           <t>Inflacion observada hasta</t>
         </is>
       </c>
-      <c r="B124" s="13" t="inlineStr">
+      <c r="B127" s="16" t="inlineStr">
         <is>
           <t>202605</t>
         </is>
       </c>
-      <c r="C124" s="14" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="12" t="inlineStr">
+      <c r="C127" s="17" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="15" t="inlineStr">
         <is>
           <t>Proyeccion BCRP desde</t>
         </is>
       </c>
-      <c r="B125" s="13" t="inlineStr">
+      <c r="B128" s="16" t="inlineStr">
         <is>
           <t>202606</t>
         </is>
       </c>
-      <c r="C125" s="14" t="inlineStr">
+      <c r="C128" s="17" t="inlineStr">
         <is>
           <t>tres escenarios</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:K113"/>
+  <autoFilter ref="A5:N113"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>